--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.82438317461282</v>
+        <v>4.033962265874584</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1655391116612</v>
+        <v>4.089400105644946</v>
       </c>
       <c r="E2" t="n">
-        <v>22.64921841810332</v>
+        <v>3.68049799294179</v>
       </c>
       <c r="F2" t="n">
-        <v>11.32143232184722</v>
+        <v>1.839732752300173</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.95559270261194</v>
+        <v>2.43028381417444</v>
       </c>
       <c r="D3" t="n">
-        <v>14.66585925077757</v>
+        <v>2.383202128251354</v>
       </c>
       <c r="E3" t="n">
-        <v>22.64921841810332</v>
+        <v>3.68049799294179</v>
       </c>
       <c r="F3" t="n">
-        <v>11.32143232184722</v>
+        <v>1.839732752300173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>81.20684151691121</v>
+        <v>13.19611174649807</v>
       </c>
       <c r="D4" t="n">
-        <v>47.54575986081245</v>
+        <v>7.726185977382023</v>
       </c>
       <c r="E4" t="n">
-        <v>22.64921841810332</v>
+        <v>3.68049799294179</v>
       </c>
       <c r="F4" t="n">
-        <v>11.32143232184722</v>
+        <v>1.839732752300173</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.75386873230305</v>
+        <v>5.972503668999247</v>
       </c>
       <c r="D5" t="n">
-        <v>36.10994113317189</v>
+        <v>5.867865434140432</v>
       </c>
       <c r="E5" t="n">
-        <v>22.64921841810332</v>
+        <v>3.68049799294179</v>
       </c>
       <c r="F5" t="n">
-        <v>11.32143232184722</v>
+        <v>1.839732752300173</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.00395141065283</v>
+        <v>6.338142104231085</v>
       </c>
       <c r="D6" t="n">
-        <v>37.9623636924082</v>
+        <v>6.168884100016333</v>
       </c>
       <c r="E6" t="n">
-        <v>22.64921841810332</v>
+        <v>3.68049799294179</v>
       </c>
       <c r="F6" t="n">
-        <v>11.32143232184722</v>
+        <v>1.839732752300173</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
